--- a/data/raw/correct_score_odds.xlsx
+++ b/data/raw/correct_score_odds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC RACING\Desktop\Proyecto Correct Score\CorrectScoreLab\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46F0A8C-456C-4D9C-8643-5450103F3194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E3BFCF-22BC-4C88-AE18-832EF2A40213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E55D949-93A9-4112-B072-7E899236BF42}"/>
   </bookViews>

--- a/data/raw/correct_score_odds.xlsx
+++ b/data/raw/correct_score_odds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC RACING\Desktop\Proyecto Correct Score\CorrectScoreLab\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E3BFCF-22BC-4C88-AE18-832EF2A40213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B8429B-4F01-4021-9497-A9507E9592CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E55D949-93A9-4112-B072-7E899236BF42}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="10" xr2:uid="{7E55D949-93A9-4112-B072-7E899236BF42}"/>
   </bookViews>
   <sheets>
     <sheet name="ESP_2021" sheetId="1" r:id="rId1"/>
@@ -642,7 +642,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -678,6 +678,7 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -9810,9 +9811,10 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9831,7 +9833,7 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
     </row>
@@ -9851,6 +9853,9 @@
       <c r="E2" t="s">
         <v>14</v>
       </c>
+      <c r="F2" s="13">
+        <v>21</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
@@ -9868,6 +9873,9 @@
       <c r="E3" t="s">
         <v>52</v>
       </c>
+      <c r="F3" s="13">
+        <v>56</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
@@ -9885,6 +9893,9 @@
       <c r="E4" t="s">
         <v>34</v>
       </c>
+      <c r="F4" s="13">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
@@ -9902,6 +9913,9 @@
       <c r="E5" t="s">
         <v>39</v>
       </c>
+      <c r="F5" s="13">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
@@ -9919,6 +9933,9 @@
       <c r="E6" t="s">
         <v>17</v>
       </c>
+      <c r="F6" s="13">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
@@ -9936,6 +9953,9 @@
       <c r="E7" t="s">
         <v>31</v>
       </c>
+      <c r="F7" s="13">
+        <v>7</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
@@ -9953,6 +9973,9 @@
       <c r="E8" t="s">
         <v>53</v>
       </c>
+      <c r="F8" s="13">
+        <v>46</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
@@ -9970,6 +9993,9 @@
       <c r="E9" t="s">
         <v>41</v>
       </c>
+      <c r="F9" s="13">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
@@ -9987,6 +10013,9 @@
       <c r="E10" t="s">
         <v>35</v>
       </c>
+      <c r="F10" s="13">
+        <v>61</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
@@ -10004,6 +10033,9 @@
       <c r="E11" t="s">
         <v>31</v>
       </c>
+      <c r="F11" s="13">
+        <v>17</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
@@ -10021,6 +10053,9 @@
       <c r="E12" t="s">
         <v>14</v>
       </c>
+      <c r="F12" s="13">
+        <v>8</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
@@ -10038,6 +10073,9 @@
       <c r="E13" t="s">
         <v>54</v>
       </c>
+      <c r="F13" s="13">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
@@ -10055,6 +10093,9 @@
       <c r="E14" t="s">
         <v>49</v>
       </c>
+      <c r="F14" s="13">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
@@ -10072,6 +10113,9 @@
       <c r="E15" t="s">
         <v>14</v>
       </c>
+      <c r="F15" s="13">
+        <v>11</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
@@ -10089,8 +10133,11 @@
       <c r="E16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>44429</v>
       </c>
@@ -10106,8 +10153,11 @@
       <c r="E17" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>44430</v>
       </c>
@@ -10123,8 +10173,11 @@
       <c r="E18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>44430</v>
       </c>
@@ -10140,8 +10193,11 @@
       <c r="E19" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>44430</v>
       </c>
@@ -10157,8 +10213,11 @@
       <c r="E20" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>44431</v>
       </c>
@@ -10174,8 +10233,11 @@
       <c r="E21" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>44436</v>
       </c>
@@ -10191,8 +10253,11 @@
       <c r="E22" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>44436</v>
       </c>
@@ -10208,8 +10273,11 @@
       <c r="E23" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>44436</v>
       </c>
@@ -10225,8 +10293,11 @@
       <c r="E24" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>44436</v>
       </c>
@@ -10242,8 +10313,11 @@
       <c r="E25" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>44436</v>
       </c>
@@ -10259,8 +10333,11 @@
       <c r="E26" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>44436</v>
       </c>
@@ -10276,8 +10353,11 @@
       <c r="E27" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>44436</v>
       </c>
@@ -10293,8 +10373,11 @@
       <c r="E28" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>44437</v>
       </c>
@@ -10310,8 +10393,11 @@
       <c r="E29" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>44437</v>
       </c>
@@ -10327,8 +10413,11 @@
       <c r="E30" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>44437</v>
       </c>
@@ -10344,8 +10433,11 @@
       <c r="E31" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>44450</v>
       </c>
@@ -10361,8 +10453,11 @@
       <c r="E32" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>44450</v>
       </c>
@@ -10378,8 +10473,11 @@
       <c r="E33" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>44450</v>
       </c>
@@ -10395,8 +10493,11 @@
       <c r="E34" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>44450</v>
       </c>
@@ -10412,8 +10513,11 @@
       <c r="E35" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>44450</v>
       </c>
@@ -10429,8 +10533,11 @@
       <c r="E36" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>44450</v>
       </c>
@@ -10446,8 +10553,11 @@
       <c r="E37" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>44450</v>
       </c>
@@ -10463,8 +10573,11 @@
       <c r="E38" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38" s="13">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>44450</v>
       </c>
@@ -10480,8 +10593,11 @@
       <c r="E39" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>44451</v>
       </c>
@@ -10497,8 +10613,11 @@
       <c r="E40" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>44452</v>
       </c>
@@ -10514,8 +10633,11 @@
       <c r="E41" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>44456</v>
       </c>
@@ -10531,8 +10653,11 @@
       <c r="E42" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>44457</v>
       </c>
@@ -10548,8 +10673,11 @@
       <c r="E43" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
         <v>44457</v>
       </c>
@@ -10565,8 +10693,11 @@
       <c r="E44" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
         <v>44457</v>
       </c>
@@ -10582,8 +10713,11 @@
       <c r="E45" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
         <v>44457</v>
       </c>
@@ -10599,8 +10733,11 @@
       <c r="E46" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>44457</v>
       </c>
@@ -10616,8 +10753,11 @@
       <c r="E47" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>44457</v>
       </c>
@@ -10633,8 +10773,11 @@
       <c r="E48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>44458</v>
       </c>
@@ -10650,8 +10793,11 @@
       <c r="E49" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <v>44458</v>
       </c>
@@ -10667,8 +10813,11 @@
       <c r="E50" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F50" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>44458</v>
       </c>
@@ -10684,8 +10833,11 @@
       <c r="E51" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F51" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>44464</v>
       </c>
@@ -10701,8 +10853,11 @@
       <c r="E52" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F52" s="13">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>44464</v>
       </c>
@@ -10718,8 +10873,11 @@
       <c r="E53" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F53" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>44464</v>
       </c>
@@ -10735,8 +10893,11 @@
       <c r="E54" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F54" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>44464</v>
       </c>
@@ -10752,8 +10913,11 @@
       <c r="E55" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>44464</v>
       </c>
@@ -10769,8 +10933,11 @@
       <c r="E56" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>44464</v>
       </c>
@@ -10786,8 +10953,11 @@
       <c r="E57" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F57" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <v>44464</v>
       </c>
@@ -10803,8 +10973,11 @@
       <c r="E58" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F58" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>44465</v>
       </c>
@@ -10820,8 +10993,11 @@
       <c r="E59" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F59" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>44465</v>
       </c>
@@ -10837,8 +11013,11 @@
       <c r="E60" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F60" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>44466</v>
       </c>
@@ -10854,8 +11033,11 @@
       <c r="E61" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F61" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>44471</v>
       </c>
@@ -10871,8 +11053,11 @@
       <c r="E62" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F62" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>44471</v>
       </c>
@@ -10888,8 +11073,11 @@
       <c r="E63" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F63" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <v>44471</v>
       </c>
@@ -10905,8 +11093,11 @@
       <c r="E64" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F64" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>44471</v>
       </c>
@@ -10922,8 +11113,11 @@
       <c r="E65" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F65" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>44471</v>
       </c>
@@ -10939,8 +11133,11 @@
       <c r="E66" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F66" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>44471</v>
       </c>
@@ -10956,8 +11153,11 @@
       <c r="E67" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F67" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>44472</v>
       </c>
@@ -10973,8 +11173,11 @@
       <c r="E68" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F68" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
         <v>44472</v>
       </c>
@@ -10990,8 +11193,11 @@
       <c r="E69" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F69" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
         <v>44472</v>
       </c>
@@ -11007,8 +11213,11 @@
       <c r="E70" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F70" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>44472</v>
       </c>
@@ -11024,8 +11233,11 @@
       <c r="E71" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F71" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>44485</v>
       </c>
@@ -11041,8 +11253,11 @@
       <c r="E72" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F72" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>44485</v>
       </c>
@@ -11058,8 +11273,11 @@
       <c r="E73" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F73" s="13">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>44485</v>
       </c>
@@ -11075,8 +11293,11 @@
       <c r="E74" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F74" s="13">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <v>44485</v>
       </c>
@@ -11092,8 +11313,11 @@
       <c r="E75" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F75" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <v>44485</v>
       </c>
@@ -11109,8 +11333,11 @@
       <c r="E76" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F76" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>44485</v>
       </c>
@@ -11126,8 +11353,11 @@
       <c r="E77" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F77" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>44485</v>
       </c>
@@ -11143,8 +11373,11 @@
       <c r="E78" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F78" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>44486</v>
       </c>
@@ -11160,8 +11393,11 @@
       <c r="E79" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F79" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>44486</v>
       </c>
@@ -11177,8 +11413,11 @@
       <c r="E80" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F80" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <v>44487</v>
       </c>
@@ -11194,8 +11433,11 @@
       <c r="E81" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F81" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <v>44491</v>
       </c>
@@ -11211,8 +11453,11 @@
       <c r="E82" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F82" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <v>44492</v>
       </c>
@@ -11228,8 +11473,11 @@
       <c r="E83" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F83" s="13">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>44492</v>
       </c>
@@ -11245,8 +11493,11 @@
       <c r="E84" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F84" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>44492</v>
       </c>
@@ -11262,8 +11513,11 @@
       <c r="E85" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F85" s="13">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <v>44492</v>
       </c>
@@ -11279,8 +11533,11 @@
       <c r="E86" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F86" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>44492</v>
       </c>
@@ -11296,8 +11553,11 @@
       <c r="E87" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F87" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
         <v>44492</v>
       </c>
@@ -11313,8 +11573,11 @@
       <c r="E88" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F88" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="9">
         <v>44493</v>
       </c>
@@ -11330,8 +11593,11 @@
       <c r="E89" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F89" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="9">
         <v>44493</v>
       </c>
@@ -11347,8 +11613,11 @@
       <c r="E90" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F90" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="9">
         <v>44493</v>
       </c>
@@ -11364,8 +11633,11 @@
       <c r="E91" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F91" s="13">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="9">
         <v>44499</v>
       </c>
@@ -11381,8 +11653,11 @@
       <c r="E92" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F92" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="9">
         <v>44499</v>
       </c>
@@ -11398,8 +11673,11 @@
       <c r="E93" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F93" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="9">
         <v>44499</v>
       </c>
@@ -11415,8 +11693,11 @@
       <c r="E94" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F94" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="9">
         <v>44499</v>
       </c>
@@ -11432,8 +11713,11 @@
       <c r="E95" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F95" s="13">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
         <v>44499</v>
       </c>
@@ -11449,8 +11733,11 @@
       <c r="E96" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F96" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="9">
         <v>44499</v>
       </c>
@@ -11466,8 +11753,11 @@
       <c r="E97" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F97" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="9">
         <v>44499</v>
       </c>
@@ -11483,8 +11773,11 @@
       <c r="E98" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F98" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="9">
         <v>44500</v>
       </c>
@@ -11500,8 +11793,11 @@
       <c r="E99" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F99" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="9">
         <v>44500</v>
       </c>
@@ -11517,8 +11813,11 @@
       <c r="E100" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F100" s="13">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="9">
         <v>44501</v>
       </c>
@@ -11534,8 +11833,11 @@
       <c r="E101" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F101" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="9">
         <v>44505</v>
       </c>
@@ -11551,8 +11853,11 @@
       <c r="E102" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F102" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="9">
         <v>44506</v>
       </c>
@@ -11568,8 +11873,11 @@
       <c r="E103" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F103" s="13">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
         <v>44506</v>
       </c>
@@ -11585,8 +11893,11 @@
       <c r="E104" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F104" s="13">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="9">
         <v>44506</v>
       </c>
@@ -11602,8 +11913,11 @@
       <c r="E105" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F105" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="9">
         <v>44506</v>
       </c>
@@ -11619,8 +11933,11 @@
       <c r="E106" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F106" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
         <v>44506</v>
       </c>
@@ -11636,8 +11953,11 @@
       <c r="E107" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F107" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="9">
         <v>44507</v>
       </c>
@@ -11653,8 +11973,11 @@
       <c r="E108" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F108" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
         <v>44507</v>
       </c>
@@ -11670,8 +11993,11 @@
       <c r="E109" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F109" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="9">
         <v>44507</v>
       </c>
@@ -11687,8 +12013,11 @@
       <c r="E110" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F110" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="9">
         <v>44507</v>
       </c>
@@ -11704,8 +12033,11 @@
       <c r="E111" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F111" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="9">
         <v>44520</v>
       </c>
@@ -11721,8 +12053,11 @@
       <c r="E112" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F112" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="9">
         <v>44520</v>
       </c>
@@ -11738,8 +12073,11 @@
       <c r="E113" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F113" s="13">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="9">
         <v>44520</v>
       </c>
@@ -11755,8 +12093,11 @@
       <c r="E114" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F114" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="9">
         <v>44520</v>
       </c>
@@ -11772,8 +12113,11 @@
       <c r="E115" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F115" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="9">
         <v>44520</v>
       </c>
@@ -11789,8 +12133,11 @@
       <c r="E116" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F116" s="13">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="9">
         <v>44520</v>
       </c>
@@ -11806,8 +12153,11 @@
       <c r="E117" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F117" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="9">
         <v>44520</v>
       </c>
@@ -11823,8 +12173,11 @@
       <c r="E118" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F118" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="9">
         <v>44520</v>
       </c>
@@ -11840,8 +12193,11 @@
       <c r="E119" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F119" s="13">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="9">
         <v>44521</v>
       </c>
@@ -11857,8 +12213,11 @@
       <c r="E120" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F120" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="9">
         <v>44521</v>
       </c>
@@ -11874,8 +12233,11 @@
       <c r="E121" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F121" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="9">
         <v>44527</v>
       </c>
@@ -11891,8 +12253,11 @@
       <c r="E122" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F122" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="9">
         <v>44527</v>
       </c>
@@ -11908,8 +12273,11 @@
       <c r="E123" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F123" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="9">
         <v>44527</v>
       </c>
@@ -11925,8 +12293,11 @@
       <c r="E124" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F124" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="9">
         <v>44527</v>
       </c>
@@ -11942,8 +12313,11 @@
       <c r="E125" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F125" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="9">
         <v>44527</v>
       </c>
@@ -11959,8 +12333,11 @@
       <c r="E126" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F126" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="9">
         <v>44528</v>
       </c>
@@ -11976,8 +12353,11 @@
       <c r="E127" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F127" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="9">
         <v>44528</v>
       </c>
@@ -11993,8 +12373,11 @@
       <c r="E128" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F128" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="9">
         <v>44528</v>
       </c>
@@ -12010,8 +12393,11 @@
       <c r="E129" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F129" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="9">
         <v>44528</v>
       </c>
@@ -12027,8 +12413,11 @@
       <c r="E130" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F130" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="9">
         <v>44530</v>
       </c>
@@ -12044,8 +12433,11 @@
       <c r="E131" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F131" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="9">
         <v>44530</v>
       </c>
@@ -12061,8 +12453,11 @@
       <c r="E132" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F132" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="9">
         <v>44531</v>
       </c>
@@ -12078,8 +12473,11 @@
       <c r="E133" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F133" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="9">
         <v>44531</v>
       </c>
@@ -12095,8 +12493,11 @@
       <c r="E134" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F134" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="9">
         <v>44531</v>
       </c>
@@ -12112,8 +12513,11 @@
       <c r="E135" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F135" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="9">
         <v>44531</v>
       </c>
@@ -12129,8 +12533,11 @@
       <c r="E136" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F136" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="9">
         <v>44531</v>
       </c>
@@ -12146,8 +12553,11 @@
       <c r="E137" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F137" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="9">
         <v>44531</v>
       </c>
@@ -12163,8 +12573,11 @@
       <c r="E138" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F138" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="9">
         <v>44532</v>
       </c>
@@ -12180,8 +12593,11 @@
       <c r="E139" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F139" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="9">
         <v>44532</v>
       </c>
@@ -12197,8 +12613,11 @@
       <c r="E140" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F140" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="9">
         <v>44534</v>
       </c>
@@ -12214,8 +12633,11 @@
       <c r="E141" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F141" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="9">
         <v>44534</v>
       </c>
@@ -12231,8 +12653,11 @@
       <c r="E142" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F142" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="9">
         <v>44534</v>
       </c>
@@ -12248,8 +12673,11 @@
       <c r="E143" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F143" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="9">
         <v>44534</v>
       </c>
@@ -12265,8 +12693,11 @@
       <c r="E144" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F144" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="9">
         <v>44534</v>
       </c>
@@ -12282,8 +12713,11 @@
       <c r="E145" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F145" s="13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="9">
         <v>44535</v>
       </c>
@@ -12299,8 +12733,11 @@
       <c r="E146" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F146" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="9">
         <v>44535</v>
       </c>
@@ -12316,8 +12753,11 @@
       <c r="E147" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F147" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="9">
         <v>44535</v>
       </c>
@@ -12333,8 +12773,11 @@
       <c r="E148" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F148" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="9">
         <v>44535</v>
       </c>
@@ -12350,8 +12793,11 @@
       <c r="E149" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F149" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="9">
         <v>44536</v>
       </c>
@@ -12367,8 +12813,11 @@
       <c r="E150" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F150" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="9">
         <v>44540</v>
       </c>
@@ -12384,8 +12833,11 @@
       <c r="E151" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F151" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="9">
         <v>44541</v>
       </c>
@@ -12401,8 +12853,11 @@
       <c r="E152" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F152" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="9">
         <v>44541</v>
       </c>
@@ -12418,8 +12873,11 @@
       <c r="E153" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F153" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="9">
         <v>44541</v>
       </c>
@@ -12435,8 +12893,11 @@
       <c r="E154" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F154" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="9">
         <v>44541</v>
       </c>
@@ -12452,8 +12913,11 @@
       <c r="E155" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F155" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="9">
         <v>44541</v>
       </c>
@@ -12469,8 +12933,11 @@
       <c r="E156" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F156" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="9">
         <v>44542</v>
       </c>
@@ -12486,8 +12953,11 @@
       <c r="E157" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F157" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="9">
         <v>44542</v>
       </c>
@@ -12503,8 +12973,11 @@
       <c r="E158" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F158" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="9">
         <v>44542</v>
       </c>
@@ -12520,8 +12993,11 @@
       <c r="E159" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F159" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="9">
         <v>44544</v>
       </c>
@@ -12537,8 +13013,11 @@
       <c r="E160" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F160" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="9">
         <v>44544</v>
       </c>
@@ -12554,8 +13033,11 @@
       <c r="E161" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F161" s="13">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="9">
         <v>44545</v>
       </c>
@@ -12571,8 +13053,11 @@
       <c r="E162" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F162" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="9">
         <v>44545</v>
       </c>
@@ -12588,8 +13073,11 @@
       <c r="E163" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F163" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="9">
         <v>44545</v>
       </c>
@@ -12605,8 +13093,11 @@
       <c r="E164" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F164" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="9">
         <v>44546</v>
       </c>
@@ -12622,8 +13113,11 @@
       <c r="E165" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F165" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="9">
         <v>44546</v>
       </c>
@@ -12639,8 +13133,11 @@
       <c r="E166" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F166" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="9">
         <v>44548</v>
       </c>
@@ -12656,8 +13153,11 @@
       <c r="E167" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F167" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="9">
         <v>44549</v>
       </c>
@@ -12673,8 +13173,11 @@
       <c r="E168" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F168" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="9">
         <v>44549</v>
       </c>
@@ -12690,8 +13193,11 @@
       <c r="E169" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F169" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="9">
         <v>44549</v>
       </c>
@@ -12707,8 +13213,11 @@
       <c r="E170" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F170" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="9">
         <v>44556</v>
       </c>
@@ -12724,8 +13233,11 @@
       <c r="E171" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F171" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="9">
         <v>44556</v>
       </c>
@@ -12741,8 +13253,11 @@
       <c r="E172" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F172" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="9">
         <v>44556</v>
       </c>
@@ -12758,8 +13273,11 @@
       <c r="E173" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F173" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="9">
         <v>44556</v>
       </c>
@@ -12775,8 +13293,11 @@
       <c r="E174" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F174" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="9">
         <v>44556</v>
       </c>
@@ -12792,8 +13313,11 @@
       <c r="E175" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F175" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="9">
         <v>44556</v>
       </c>
@@ -12809,8 +13333,11 @@
       <c r="E176" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F176" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="9">
         <v>44557</v>
       </c>
@@ -12826,8 +13353,11 @@
       <c r="E177" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F177" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="9">
         <v>44558</v>
       </c>
@@ -12843,8 +13373,11 @@
       <c r="E178" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F178" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="9">
         <v>44558</v>
       </c>
@@ -12860,8 +13393,11 @@
       <c r="E179" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F179" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="9">
         <v>44558</v>
       </c>
@@ -12877,8 +13413,11 @@
       <c r="E180" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F180" s="13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="9">
         <v>44558</v>
       </c>
@@ -12894,8 +13433,11 @@
       <c r="E181" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F181" s="13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="9">
         <v>44559</v>
       </c>
@@ -12911,8 +13453,11 @@
       <c r="E182" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F182" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="9">
         <v>44559</v>
       </c>
@@ -12928,8 +13473,11 @@
       <c r="E183" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F183" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="9">
         <v>44560</v>
       </c>
@@ -12945,8 +13493,11 @@
       <c r="E184" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F184" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="9">
         <v>44562</v>
       </c>
@@ -12962,8 +13513,11 @@
       <c r="E185" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F185" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="9">
         <v>44562</v>
       </c>
@@ -12979,8 +13533,11 @@
       <c r="E186" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F186" s="13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="9">
         <v>44562</v>
       </c>
@@ -12996,8 +13553,11 @@
       <c r="E187" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F187" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="9">
         <v>44563</v>
       </c>
@@ -13013,8 +13573,11 @@
       <c r="E188" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F188" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="9">
         <v>44563</v>
       </c>
@@ -13030,8 +13593,11 @@
       <c r="E189" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F189" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="9">
         <v>44563</v>
       </c>
@@ -13047,8 +13613,11 @@
       <c r="E190" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F190" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="9">
         <v>44563</v>
       </c>
@@ -13064,8 +13633,11 @@
       <c r="E191" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F191" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="9">
         <v>44564</v>
       </c>
@@ -13081,8 +13653,11 @@
       <c r="E192" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F192" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="9">
         <v>44572</v>
       </c>
@@ -13098,8 +13673,11 @@
       <c r="E193" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F193" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="9">
         <v>44573</v>
       </c>
@@ -13115,8 +13693,11 @@
       <c r="E194" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F194" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="9">
         <v>44575</v>
       </c>
@@ -13132,8 +13713,11 @@
       <c r="E195" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F195" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="9">
         <v>44576</v>
       </c>
@@ -13149,8 +13733,11 @@
       <c r="E196" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F196" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="9">
         <v>44576</v>
       </c>
@@ -13166,8 +13753,11 @@
       <c r="E197" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F197" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="9">
         <v>44576</v>
       </c>
@@ -13183,8 +13773,11 @@
       <c r="E198" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F198" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="9">
         <v>44576</v>
       </c>
@@ -13200,8 +13793,11 @@
       <c r="E199" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F199" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="9">
         <v>44576</v>
       </c>
@@ -13217,8 +13813,11 @@
       <c r="E200" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F200" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="9">
         <v>44577</v>
       </c>
@@ -13234,8 +13833,11 @@
       <c r="E201" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F201" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="9">
         <v>44577</v>
       </c>
@@ -13251,8 +13853,11 @@
       <c r="E202" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F202" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="9">
         <v>44579</v>
       </c>
@@ -13268,8 +13873,11 @@
       <c r="E203" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F203" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="9">
         <v>44580</v>
       </c>
@@ -13285,8 +13893,11 @@
       <c r="E204" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F204" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="9">
         <v>44580</v>
       </c>
@@ -13302,8 +13913,11 @@
       <c r="E205" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F205" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="9">
         <v>44582</v>
       </c>
@@ -13319,8 +13933,11 @@
       <c r="E206" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F206" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="9">
         <v>44583</v>
       </c>
@@ -13336,8 +13953,11 @@
       <c r="E207" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F207" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="9">
         <v>44583</v>
       </c>
@@ -13353,8 +13973,11 @@
       <c r="E208" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F208" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="9">
         <v>44583</v>
       </c>
@@ -13370,8 +13993,11 @@
       <c r="E209" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F209" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="9">
         <v>44583</v>
       </c>
@@ -13387,8 +14013,11 @@
       <c r="E210" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F210" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="9">
         <v>44583</v>
       </c>
@@ -13404,8 +14033,11 @@
       <c r="E211" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F211" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="9">
         <v>44584</v>
       </c>
@@ -13421,8 +14053,11 @@
       <c r="E212" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F212" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="9">
         <v>44584</v>
       </c>
@@ -13438,8 +14073,11 @@
       <c r="E213" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F213" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="9">
         <v>44584</v>
       </c>
@@ -13455,8 +14093,11 @@
       <c r="E214" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F214" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="9">
         <v>44584</v>
       </c>
@@ -13472,8 +14113,11 @@
       <c r="E215" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F215" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="9">
         <v>44597</v>
       </c>
@@ -13489,8 +14133,11 @@
       <c r="E216" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F216" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="9">
         <v>44600</v>
       </c>
@@ -13506,8 +14153,11 @@
       <c r="E217" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F217" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="9">
         <v>44600</v>
       </c>
@@ -13523,8 +14173,11 @@
       <c r="E218" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F218" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="9">
         <v>44600</v>
       </c>
@@ -13540,8 +14193,11 @@
       <c r="E219" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F219" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="9">
         <v>44601</v>
       </c>
@@ -13557,8 +14213,11 @@
       <c r="E220" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F220" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="9">
         <v>44601</v>
       </c>
@@ -13574,8 +14233,11 @@
       <c r="E221" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F221" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="9">
         <v>44601</v>
       </c>
@@ -13591,8 +14253,11 @@
       <c r="E222" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F222" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="9">
         <v>44601</v>
       </c>
@@ -13608,8 +14273,11 @@
       <c r="E223" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F223" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="9">
         <v>44602</v>
       </c>
@@ -13625,8 +14293,11 @@
       <c r="E224" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F224" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="9">
         <v>44602</v>
       </c>
@@ -13642,8 +14313,11 @@
       <c r="E225" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F225" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="9">
         <v>44604</v>
       </c>
@@ -13659,8 +14333,11 @@
       <c r="E226" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F226" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="9">
         <v>44604</v>
       </c>
@@ -13676,8 +14353,11 @@
       <c r="E227" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F227" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="9">
         <v>44604</v>
       </c>
@@ -13693,8 +14373,11 @@
       <c r="E228" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F228" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="9">
         <v>44604</v>
       </c>
@@ -13710,8 +14393,11 @@
       <c r="E229" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F229" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="9">
         <v>44604</v>
       </c>
@@ -13727,8 +14413,11 @@
       <c r="E230" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F230" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="9">
         <v>44605</v>
       </c>
@@ -13744,8 +14433,11 @@
       <c r="E231" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F231" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="9">
         <v>44605</v>
       </c>
@@ -13761,8 +14453,11 @@
       <c r="E232" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F232" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="9">
         <v>44605</v>
       </c>
@@ -13778,8 +14473,11 @@
       <c r="E233" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F233" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="9">
         <v>44605</v>
       </c>
@@ -13795,8 +14493,11 @@
       <c r="E234" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F234" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="9">
         <v>44607</v>
       </c>
@@ -13812,8 +14513,11 @@
       <c r="E235" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F235" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="9">
         <v>44611</v>
       </c>
@@ -13829,8 +14533,11 @@
       <c r="E236" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F236" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="9">
         <v>44611</v>
       </c>
@@ -13846,8 +14553,11 @@
       <c r="E237" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F237" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="9">
         <v>44611</v>
       </c>
@@ -13863,8 +14573,11 @@
       <c r="E238" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F238" s="13">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="9">
         <v>44611</v>
       </c>
@@ -13880,8 +14593,11 @@
       <c r="E239" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F239" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="9">
         <v>44611</v>
       </c>
@@ -13897,8 +14613,11 @@
       <c r="E240" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F240" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="9">
         <v>44611</v>
       </c>
@@ -13914,8 +14633,11 @@
       <c r="E241" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F241" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="9">
         <v>44611</v>
       </c>
@@ -13931,8 +14653,11 @@
       <c r="E242" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F242" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="9">
         <v>44611</v>
       </c>
@@ -13948,8 +14673,11 @@
       <c r="E243" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F243" s="13">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="9">
         <v>44612</v>
       </c>
@@ -13965,8 +14693,11 @@
       <c r="E244" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F244" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="9">
         <v>44612</v>
       </c>
@@ -13982,8 +14713,11 @@
       <c r="E245" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F245" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="9">
         <v>44615</v>
       </c>
@@ -13999,8 +14733,11 @@
       <c r="E246" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F246" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="9">
         <v>44615</v>
       </c>
@@ -14016,8 +14753,11 @@
       <c r="E247" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F247" s="13">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="9">
         <v>44615</v>
       </c>
@@ -14033,8 +14773,11 @@
       <c r="E248" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F248" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="9">
         <v>44616</v>
       </c>
@@ -14050,8 +14793,11 @@
       <c r="E249" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F249" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="9">
         <v>44617</v>
       </c>
@@ -14067,8 +14813,11 @@
       <c r="E250" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F250" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="9">
         <v>44618</v>
       </c>
@@ -14084,8 +14833,11 @@
       <c r="E251" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F251" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="9">
         <v>44618</v>
       </c>
@@ -14101,8 +14853,11 @@
       <c r="E252" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F252" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="9">
         <v>44618</v>
       </c>
@@ -14118,8 +14873,11 @@
       <c r="E253" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F253" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="9">
         <v>44618</v>
       </c>
@@ -14135,8 +14893,11 @@
       <c r="E254" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F254" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="9">
         <v>44618</v>
       </c>
@@ -14152,8 +14913,11 @@
       <c r="E255" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F255" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="9">
         <v>44618</v>
       </c>
@@ -14169,8 +14933,11 @@
       <c r="E256" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F256" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="9">
         <v>44619</v>
       </c>
@@ -14186,8 +14953,11 @@
       <c r="E257" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F257" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="9">
         <v>44621</v>
       </c>
@@ -14203,8 +14973,11 @@
       <c r="E258" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F258" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="9">
         <v>44625</v>
       </c>
@@ -14220,8 +14993,11 @@
       <c r="E259" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F259" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="9">
         <v>44625</v>
       </c>
@@ -14237,8 +15013,11 @@
       <c r="E260" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F260" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="9">
         <v>44625</v>
       </c>
@@ -14254,8 +15033,11 @@
       <c r="E261" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F261" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="9">
         <v>44625</v>
       </c>
@@ -14271,8 +15053,11 @@
       <c r="E262" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F262" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="9">
         <v>44625</v>
       </c>
@@ -14288,8 +15073,11 @@
       <c r="E263" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F263" s="13">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="9">
         <v>44625</v>
       </c>
@@ -14305,8 +15093,11 @@
       <c r="E264" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F264" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="9">
         <v>44625</v>
       </c>
@@ -14322,8 +15113,11 @@
       <c r="E265" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F265" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="9">
         <v>44626</v>
       </c>
@@ -14339,8 +15133,11 @@
       <c r="E266" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F266" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="9">
         <v>44626</v>
       </c>
@@ -14356,8 +15153,11 @@
       <c r="E267" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F267" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="9">
         <v>44627</v>
       </c>
@@ -14373,8 +15173,11 @@
       <c r="E268" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F268" s="13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="9">
         <v>44630</v>
       </c>
@@ -14390,8 +15193,11 @@
       <c r="E269" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F269" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="9">
         <v>44630</v>
       </c>
@@ -14407,8 +15213,11 @@
       <c r="E270" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F270" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="9">
         <v>44630</v>
       </c>
@@ -14424,8 +15233,11 @@
       <c r="E271" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F271" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="9">
         <v>44630</v>
       </c>
@@ -14441,8 +15253,11 @@
       <c r="E272" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F272" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="9">
         <v>44632</v>
       </c>
@@ -14458,8 +15273,11 @@
       <c r="E273" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F273" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="9">
         <v>44632</v>
       </c>
@@ -14475,8 +15293,11 @@
       <c r="E274" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F274" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="9">
         <v>44632</v>
       </c>
@@ -14492,8 +15313,11 @@
       <c r="E275" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F275" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="9">
         <v>44633</v>
       </c>
@@ -14509,8 +15333,11 @@
       <c r="E276" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F276" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="9">
         <v>44633</v>
       </c>
@@ -14526,8 +15353,11 @@
       <c r="E277" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F277" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="9">
         <v>44633</v>
       </c>
@@ -14543,8 +15373,11 @@
       <c r="E278" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F278" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="9">
         <v>44633</v>
       </c>
@@ -14560,8 +15393,11 @@
       <c r="E279" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F279" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="9">
         <v>44633</v>
       </c>
@@ -14577,8 +15413,11 @@
       <c r="E280" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F280" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="9">
         <v>44633</v>
       </c>
@@ -14594,8 +15433,11 @@
       <c r="E281" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F281" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="9">
         <v>44634</v>
       </c>
@@ -14611,8 +15453,11 @@
       <c r="E282" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F282" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="9">
         <v>44636</v>
       </c>
@@ -14628,8 +15473,11 @@
       <c r="E283" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F283" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="9">
         <v>44636</v>
       </c>
@@ -14645,8 +15493,11 @@
       <c r="E284" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F284" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="9">
         <v>44637</v>
       </c>
@@ -14662,8 +15513,11 @@
       <c r="E285" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F285" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="9">
         <v>44638</v>
       </c>
@@ -14679,8 +15533,11 @@
       <c r="E286" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F286" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="9">
         <v>44639</v>
       </c>
@@ -14696,8 +15553,11 @@
       <c r="E287" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F287" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="9">
         <v>44640</v>
       </c>
@@ -14713,8 +15573,11 @@
       <c r="E288" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F288" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="9">
         <v>44640</v>
       </c>
@@ -14730,8 +15593,11 @@
       <c r="E289" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F289" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="9">
         <v>44653</v>
       </c>
@@ -14747,8 +15613,11 @@
       <c r="E290" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F290" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="9">
         <v>44653</v>
       </c>
@@ -14764,8 +15633,11 @@
       <c r="E291" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F291" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="9">
         <v>44653</v>
       </c>
@@ -14781,8 +15653,11 @@
       <c r="E292" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F292" s="13">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="9">
         <v>44653</v>
       </c>
@@ -14798,8 +15673,11 @@
       <c r="E293" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F293" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="9">
         <v>44653</v>
       </c>
@@ -14815,8 +15693,11 @@
       <c r="E294" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F294" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="9">
         <v>44653</v>
       </c>
@@ -14832,8 +15713,11 @@
       <c r="E295" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F295" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="9">
         <v>44653</v>
       </c>
@@ -14849,8 +15733,11 @@
       <c r="E296" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F296" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="9">
         <v>44654</v>
       </c>
@@ -14866,8 +15753,11 @@
       <c r="E297" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F297" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="9">
         <v>44654</v>
       </c>
@@ -14883,8 +15773,11 @@
       <c r="E298" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F298" s="13">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="9">
         <v>44655</v>
       </c>
@@ -14900,8 +15793,11 @@
       <c r="E299" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F299" s="13">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="9">
         <v>44657</v>
       </c>
@@ -14917,8 +15813,11 @@
       <c r="E300" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F300" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="9">
         <v>44659</v>
       </c>
@@ -14934,8 +15833,11 @@
       <c r="E301" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F301" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="9">
         <v>44660</v>
       </c>
@@ -14951,8 +15853,11 @@
       <c r="E302" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F302" s="13">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="9">
         <v>44660</v>
       </c>
@@ -14968,8 +15873,11 @@
       <c r="E303" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F303" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="9">
         <v>44660</v>
       </c>
@@ -14985,8 +15893,11 @@
       <c r="E304" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F304" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="9">
         <v>44660</v>
       </c>
@@ -15002,8 +15913,11 @@
       <c r="E305" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F305" s="13">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="9">
         <v>44660</v>
       </c>
@@ -15019,8 +15933,11 @@
       <c r="E306" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F306" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="9">
         <v>44661</v>
       </c>
@@ -15036,8 +15953,11 @@
       <c r="E307" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F307" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="9">
         <v>44661</v>
       </c>
@@ -15053,8 +15973,11 @@
       <c r="E308" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F308" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="9">
         <v>44661</v>
       </c>
@@ -15070,8 +15993,11 @@
       <c r="E309" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F309" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="9">
         <v>44661</v>
       </c>
@@ -15087,8 +16013,11 @@
       <c r="E310" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F310" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="9">
         <v>44667</v>
       </c>
@@ -15104,8 +16033,11 @@
       <c r="E311" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F311" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="9">
         <v>44667</v>
       </c>
@@ -15121,8 +16053,11 @@
       <c r="E312" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F312" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="9">
         <v>44667</v>
       </c>
@@ -15138,8 +16073,11 @@
       <c r="E313" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F313" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="9">
         <v>44667</v>
       </c>
@@ -15155,8 +16093,11 @@
       <c r="E314" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F314" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="9">
         <v>44668</v>
       </c>
@@ -15172,8 +16113,11 @@
       <c r="E315" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F315" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="9">
         <v>44668</v>
       </c>
@@ -15189,8 +16133,11 @@
       <c r="E316" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F316" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="9">
         <v>44670</v>
       </c>
@@ -15206,8 +16153,11 @@
       <c r="E317" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F317" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="9">
         <v>44671</v>
       </c>
@@ -15223,8 +16173,11 @@
       <c r="E318" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F318" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="9">
         <v>44671</v>
       </c>
@@ -15240,8 +16193,11 @@
       <c r="E319" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F319" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="9">
         <v>44671</v>
       </c>
@@ -15257,8 +16213,11 @@
       <c r="E320" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F320" s="13">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="9">
         <v>44671</v>
       </c>
@@ -15274,8 +16233,11 @@
       <c r="E321" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F321" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="9">
         <v>44672</v>
       </c>
@@ -15291,8 +16253,11 @@
       <c r="E322" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F322" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="9">
         <v>44674</v>
       </c>
@@ -15308,8 +16273,11 @@
       <c r="E323" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F323" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="9">
         <v>44674</v>
       </c>
@@ -15325,8 +16293,11 @@
       <c r="E324" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F324" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="9">
         <v>44674</v>
       </c>
@@ -15342,8 +16313,11 @@
       <c r="E325" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F325" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="9">
         <v>44674</v>
       </c>
@@ -15359,8 +16333,11 @@
       <c r="E326" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F326" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="9">
         <v>44674</v>
       </c>
@@ -15376,8 +16353,11 @@
       <c r="E327" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F327" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="9">
         <v>44675</v>
       </c>
@@ -15393,8 +16373,11 @@
       <c r="E328" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F328" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="9">
         <v>44675</v>
       </c>
@@ -15410,8 +16393,11 @@
       <c r="E329" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F329" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="9">
         <v>44675</v>
       </c>
@@ -15427,8 +16413,11 @@
       <c r="E330" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F330" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="9">
         <v>44675</v>
       </c>
@@ -15444,8 +16433,11 @@
       <c r="E331" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F331" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="9">
         <v>44676</v>
       </c>
@@ -15461,8 +16453,11 @@
       <c r="E332" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F332" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="9">
         <v>44679</v>
       </c>
@@ -15478,8 +16473,11 @@
       <c r="E333" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F333" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="9">
         <v>44681</v>
       </c>
@@ -15495,8 +16493,11 @@
       <c r="E334" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F334" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="9">
         <v>44681</v>
       </c>
@@ -15512,8 +16513,11 @@
       <c r="E335" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F335" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="9">
         <v>44681</v>
       </c>
@@ -15529,8 +16533,11 @@
       <c r="E336" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F336" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="9">
         <v>44681</v>
       </c>
@@ -15546,8 +16553,11 @@
       <c r="E337" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F337" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="9">
         <v>44681</v>
       </c>
@@ -15563,8 +16573,11 @@
       <c r="E338" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F338" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="9">
         <v>44681</v>
       </c>
@@ -15580,8 +16593,11 @@
       <c r="E339" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F339" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="9">
         <v>44682</v>
       </c>
@@ -15597,8 +16613,11 @@
       <c r="E340" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F340" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="9">
         <v>44682</v>
       </c>
@@ -15614,8 +16633,11 @@
       <c r="E341" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F341" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="9">
         <v>44682</v>
       </c>
@@ -15631,8 +16653,11 @@
       <c r="E342" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F342" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="9">
         <v>44683</v>
       </c>
@@ -15648,8 +16673,11 @@
       <c r="E343" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F343" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="9">
         <v>44688</v>
       </c>
@@ -15665,8 +16693,11 @@
       <c r="E344" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F344" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="9">
         <v>44688</v>
       </c>
@@ -15682,8 +16713,11 @@
       <c r="E345" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F345" s="13">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="9">
         <v>44688</v>
       </c>
@@ -15699,8 +16733,11 @@
       <c r="E346" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F346" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="9">
         <v>44688</v>
       </c>
@@ -15716,8 +16753,11 @@
       <c r="E347" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F347" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="9">
         <v>44688</v>
       </c>
@@ -15733,8 +16773,11 @@
       <c r="E348" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F348" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="9">
         <v>44688</v>
       </c>
@@ -15750,8 +16793,11 @@
       <c r="E349" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F349" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="9">
         <v>44689</v>
       </c>
@@ -15767,8 +16813,11 @@
       <c r="E350" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F350" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="9">
         <v>44689</v>
       </c>
@@ -15784,8 +16833,11 @@
       <c r="E351" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F351" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="9">
         <v>44689</v>
       </c>
@@ -15801,8 +16853,11 @@
       <c r="E352" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F352" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="9">
         <v>44689</v>
       </c>
@@ -15818,8 +16873,11 @@
       <c r="E353" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F353" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="9">
         <v>44691</v>
       </c>
@@ -15835,8 +16893,11 @@
       <c r="E354" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F354" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="9">
         <v>44692</v>
       </c>
@@ -15852,8 +16913,11 @@
       <c r="E355" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F355" s="13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="9">
         <v>44692</v>
       </c>
@@ -15869,8 +16933,11 @@
       <c r="E356" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F356" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="9">
         <v>44692</v>
       </c>
@@ -15886,8 +16953,11 @@
       <c r="E357" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F357" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="9">
         <v>44692</v>
       </c>
@@ -15903,8 +16973,11 @@
       <c r="E358" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F358" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="9">
         <v>44693</v>
       </c>
@@ -15920,8 +16993,11 @@
       <c r="E359" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F359" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" s="9">
         <v>44696</v>
       </c>
@@ -15937,8 +17013,11 @@
       <c r="E360" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F360" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" s="9">
         <v>44696</v>
       </c>
@@ -15954,8 +17033,11 @@
       <c r="E361" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F361" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" s="9">
         <v>44696</v>
       </c>
@@ -15971,8 +17053,11 @@
       <c r="E362" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F362" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" s="9">
         <v>44696</v>
       </c>
@@ -15988,8 +17073,11 @@
       <c r="E363" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F363" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" s="9">
         <v>44696</v>
       </c>
@@ -16005,8 +17093,11 @@
       <c r="E364" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F364" s="13">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="9">
         <v>44696</v>
       </c>
@@ -16022,8 +17113,11 @@
       <c r="E365" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F365" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" s="9">
         <v>44696</v>
       </c>
@@ -16039,8 +17133,11 @@
       <c r="E366" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F366" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" s="9">
         <v>44697</v>
       </c>
@@ -16056,8 +17153,11 @@
       <c r="E367" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F367" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="9">
         <v>44698</v>
       </c>
@@ -16073,8 +17173,11 @@
       <c r="E368" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F368" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="9">
         <v>44700</v>
       </c>
@@ -16090,8 +17193,11 @@
       <c r="E369" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F369" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="9">
         <v>44700</v>
       </c>
@@ -16107,8 +17213,11 @@
       <c r="E370" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F370" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="9">
         <v>44700</v>
       </c>
@@ -16124,8 +17233,11 @@
       <c r="E371" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F371" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="9">
         <v>44703</v>
       </c>
@@ -16141,8 +17253,11 @@
       <c r="E372" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F372" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="9">
         <v>44703</v>
       </c>
@@ -16158,8 +17273,11 @@
       <c r="E373" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F373" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="9">
         <v>44703</v>
       </c>
@@ -16175,8 +17293,11 @@
       <c r="E374" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F374" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="9">
         <v>44703</v>
       </c>
@@ -16192,8 +17313,11 @@
       <c r="E375" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F375" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="9">
         <v>44703</v>
       </c>
@@ -16209,8 +17333,11 @@
       <c r="E376" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F376" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="9">
         <v>44703</v>
       </c>
@@ -16226,8 +17353,11 @@
       <c r="E377" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F377" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="9">
         <v>44703</v>
       </c>
@@ -16243,8 +17373,11 @@
       <c r="E378" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F378" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="9">
         <v>44703</v>
       </c>
@@ -16260,8 +17393,11 @@
       <c r="E379" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F379" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="9">
         <v>44703</v>
       </c>
@@ -16277,8 +17413,11 @@
       <c r="E380" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F380" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="9">
         <v>44703</v>
       </c>
@@ -16293,6 +17432,9 @@
       </c>
       <c r="E381" t="s">
         <v>103</v>
+      </c>
+      <c r="F381" s="13">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/correct_score_odds.xlsx
+++ b/data/raw/correct_score_odds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC RACING\Desktop\Proyecto Correct Score\CorrectScoreLab\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B8429B-4F01-4021-9497-A9507E9592CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6FCE1C-B996-4C99-AE5F-175A5B4E1ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="10" xr2:uid="{7E55D949-93A9-4112-B072-7E899236BF42}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="20" xr2:uid="{7E55D949-93A9-4112-B072-7E899236BF42}"/>
   </bookViews>
   <sheets>
     <sheet name="ESP_2021" sheetId="1" r:id="rId1"/>
@@ -38796,6 +38796,7 @@
     <col min="2" max="2" width="15.42578125" customWidth="1"/>
     <col min="3" max="4" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -38814,7 +38815,7 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
     </row>
@@ -38834,6 +38835,9 @@
       <c r="E2" t="s">
         <v>36</v>
       </c>
+      <c r="F2" s="13">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
@@ -38851,6 +38855,9 @@
       <c r="E3" t="s">
         <v>36</v>
       </c>
+      <c r="F3" s="13">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
@@ -38868,6 +38875,9 @@
       <c r="E4" t="s">
         <v>34</v>
       </c>
+      <c r="F4" s="13">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
@@ -38885,6 +38895,9 @@
       <c r="E5" t="s">
         <v>36</v>
       </c>
+      <c r="F5" s="13">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
@@ -38902,6 +38915,9 @@
       <c r="E6" t="s">
         <v>22</v>
       </c>
+      <c r="F6" s="13">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
@@ -38919,6 +38935,9 @@
       <c r="E7" t="s">
         <v>11</v>
       </c>
+      <c r="F7" s="13">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
@@ -38936,6 +38955,9 @@
       <c r="E8" t="s">
         <v>36</v>
       </c>
+      <c r="F8" s="13">
+        <v>7</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
@@ -38953,6 +38975,9 @@
       <c r="E9" t="s">
         <v>22</v>
       </c>
+      <c r="F9" s="13">
+        <v>19</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
@@ -38970,6 +38995,9 @@
       <c r="E10" t="s">
         <v>79</v>
       </c>
+      <c r="F10" s="13">
+        <v>101</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
@@ -38987,6 +39015,9 @@
       <c r="E11" t="s">
         <v>45</v>
       </c>
+      <c r="F11" s="13">
+        <v>23</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
@@ -39004,6 +39035,9 @@
       <c r="E12" t="s">
         <v>31</v>
       </c>
+      <c r="F12" s="13">
+        <v>12</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
@@ -39021,6 +39055,9 @@
       <c r="E13" t="s">
         <v>50</v>
       </c>
+      <c r="F13" s="13">
+        <v>201</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
@@ -39038,6 +39075,9 @@
       <c r="E14" t="s">
         <v>47</v>
       </c>
+      <c r="F14" s="13">
+        <v>36</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
@@ -39055,6 +39095,9 @@
       <c r="E15" t="s">
         <v>39</v>
       </c>
+      <c r="F15" s="13">
+        <v>56</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
@@ -39072,8 +39115,11 @@
       <c r="E16" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>44423</v>
       </c>
@@ -39089,8 +39135,11 @@
       <c r="E17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>44423</v>
       </c>
@@ -39106,8 +39155,11 @@
       <c r="E18" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>44423</v>
       </c>
@@ -39123,8 +39175,11 @@
       <c r="E19" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>44423</v>
       </c>
@@ -39140,8 +39195,11 @@
       <c r="E20" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>44423</v>
       </c>
@@ -39157,8 +39215,11 @@
       <c r="E21" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>44428</v>
       </c>
@@ -39174,8 +39235,11 @@
       <c r="E22" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>44429</v>
       </c>
@@ -39191,8 +39255,11 @@
       <c r="E23" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>44429</v>
       </c>
@@ -39208,8 +39275,11 @@
       <c r="E24" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>44430</v>
       </c>
@@ -39225,8 +39295,11 @@
       <c r="E25" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="13">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>44430</v>
       </c>
@@ -39242,8 +39315,11 @@
       <c r="E26" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>44430</v>
       </c>
@@ -39259,8 +39335,11 @@
       <c r="E27" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>44430</v>
       </c>
@@ -39276,8 +39355,11 @@
       <c r="E28" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>44430</v>
       </c>
@@ -39293,8 +39375,11 @@
       <c r="E29" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>44430</v>
       </c>
@@ -39310,8 +39395,11 @@
       <c r="E30" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>44435</v>
       </c>
@@ -39327,8 +39415,11 @@
       <c r="E31" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>44436</v>
       </c>
@@ -39344,8 +39435,11 @@
       <c r="E32" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>44436</v>
       </c>
@@ -39361,8 +39455,11 @@
       <c r="E33" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>44437</v>
       </c>
@@ -39378,8 +39475,11 @@
       <c r="E34" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>44437</v>
       </c>
@@ -39395,8 +39495,11 @@
       <c r="E35" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>44437</v>
       </c>
@@ -39412,8 +39515,11 @@
       <c r="E36" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>44437</v>
       </c>
@@ -39429,8 +39535,11 @@
       <c r="E37" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>44437</v>
       </c>
@@ -39446,8 +39555,11 @@
       <c r="E38" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>44437</v>
       </c>
@@ -39463,8 +39575,11 @@
       <c r="E39" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>44437</v>
       </c>
@@ -39480,8 +39595,11 @@
       <c r="E40" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40" s="13">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>44449</v>
       </c>
@@ -39497,8 +39615,11 @@
       <c r="E41" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>44450</v>
       </c>
@@ -39514,8 +39635,11 @@
       <c r="E42" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>44450</v>
       </c>
@@ -39531,8 +39655,11 @@
       <c r="E43" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
         <v>44451</v>
       </c>
@@ -39548,8 +39675,11 @@
       <c r="E44" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
         <v>44451</v>
       </c>
@@ -39565,8 +39695,11 @@
       <c r="E45" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
         <v>44451</v>
       </c>
@@ -39582,8 +39715,11 @@
       <c r="E46" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>44451</v>
       </c>
@@ -39599,8 +39735,11 @@
       <c r="E47" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>44451</v>
       </c>
@@ -39616,8 +39755,11 @@
       <c r="E48" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>44451</v>
       </c>
@@ -39633,8 +39775,11 @@
       <c r="E49" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <v>44451</v>
       </c>
@@ -39650,8 +39795,11 @@
       <c r="E50" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F50" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>44456</v>
       </c>
@@ -39667,8 +39815,11 @@
       <c r="E51" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F51" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>44457</v>
       </c>
@@ -39684,8 +39835,11 @@
       <c r="E52" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F52" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>44457</v>
       </c>
@@ -39701,8 +39855,11 @@
       <c r="E53" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F53" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>44458</v>
       </c>
@@ -39718,8 +39875,11 @@
       <c r="E54" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F54" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>44458</v>
       </c>
@@ -39735,8 +39895,11 @@
       <c r="E55" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>44458</v>
       </c>
@@ -39752,8 +39915,11 @@
       <c r="E56" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>44458</v>
       </c>
@@ -39769,8 +39935,11 @@
       <c r="E57" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F57" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <v>44458</v>
       </c>
@@ -39786,8 +39955,11 @@
       <c r="E58" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F58" s="13">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>44458</v>
       </c>
@@ -39803,8 +39975,11 @@
       <c r="E59" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F59" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>44458</v>
       </c>
@@ -39820,8 +39995,11 @@
       <c r="E60" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F60" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>44461</v>
       </c>
@@ -39837,8 +40015,11 @@
       <c r="E61" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F61" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>44461</v>
       </c>
@@ -39854,8 +40035,11 @@
       <c r="E62" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F62" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>44461</v>
       </c>
@@ -39871,8 +40055,11 @@
       <c r="E63" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F63" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <v>44461</v>
       </c>
@@ -39888,8 +40075,11 @@
       <c r="E64" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F64" s="13">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>44461</v>
       </c>
@@ -39905,8 +40095,11 @@
       <c r="E65" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F65" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>44461</v>
       </c>
@@ -39922,8 +40115,11 @@
       <c r="E66" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F66" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>44461</v>
       </c>
@@ -39939,8 +40135,11 @@
       <c r="E67" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F67" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>44461</v>
       </c>
@@ -39956,8 +40155,11 @@
       <c r="E68" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F68" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
         <v>44461</v>
       </c>
@@ -39973,8 +40175,11 @@
       <c r="E69" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F69" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
         <v>44461</v>
       </c>
@@ -39990,8 +40195,11 @@
       <c r="E70" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F70" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>44464</v>
       </c>
@@ -40007,8 +40215,11 @@
       <c r="E71" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F71" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>44464</v>
       </c>
@@ -40024,8 +40235,11 @@
       <c r="E72" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F72" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>44464</v>
       </c>
@@ -40041,8 +40255,11 @@
       <c r="E73" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F73" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>44464</v>
       </c>
@@ -40058,8 +40275,11 @@
       <c r="E74" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F74" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <v>44465</v>
       </c>
@@ -40075,8 +40295,11 @@
       <c r="E75" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F75" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <v>44465</v>
       </c>
@@ -40092,8 +40315,11 @@
       <c r="E76" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F76" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>44465</v>
       </c>
@@ -40109,8 +40335,11 @@
       <c r="E77" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F77" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>44465</v>
       </c>
@@ -40126,8 +40355,11 @@
       <c r="E78" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F78" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>44465</v>
       </c>
@@ -40143,8 +40375,11 @@
       <c r="E79" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F79" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>44465</v>
       </c>
@@ -40160,8 +40395,11 @@
       <c r="E80" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F80" s="13">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <v>44470</v>
       </c>
@@ -40177,8 +40415,11 @@
       <c r="E81" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F81" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <v>44471</v>
       </c>
@@ -40194,8 +40435,11 @@
       <c r="E82" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F82" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <v>44471</v>
       </c>
@@ -40211,8 +40455,11 @@
       <c r="E83" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F83" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>44472</v>
       </c>
@@ -40228,8 +40475,11 @@
       <c r="E84" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F84" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>44472</v>
       </c>
@@ -40245,8 +40495,11 @@
       <c r="E85" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F85" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <v>44472</v>
       </c>
@@ -40262,8 +40515,11 @@
       <c r="E86" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F86" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>44472</v>
       </c>
@@ -40279,8 +40535,11 @@
       <c r="E87" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F87" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
         <v>44472</v>
       </c>
@@ -40296,8 +40555,11 @@
       <c r="E88" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F88" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="9">
         <v>44472</v>
       </c>
@@ -40313,8 +40575,11 @@
       <c r="E89" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F89" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="9">
         <v>44472</v>
       </c>
@@ -40330,8 +40595,11 @@
       <c r="E90" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F90" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="9">
         <v>44484</v>
       </c>
@@ -40347,8 +40615,11 @@
       <c r="E91" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F91" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="9">
         <v>44485</v>
       </c>
@@ -40364,8 +40635,11 @@
       <c r="E92" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F92" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="9">
         <v>44485</v>
       </c>
@@ -40381,8 +40655,11 @@
       <c r="E93" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F93" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="9">
         <v>44486</v>
       </c>
@@ -40398,8 +40675,11 @@
       <c r="E94" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F94" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="9">
         <v>44486</v>
       </c>
@@ -40415,8 +40695,11 @@
       <c r="E95" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F95" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
         <v>44486</v>
       </c>
@@ -40432,8 +40715,11 @@
       <c r="E96" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F96" s="13">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="9">
         <v>44486</v>
       </c>
@@ -40449,8 +40735,11 @@
       <c r="E97" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F97" s="13">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="9">
         <v>44486</v>
       </c>
@@ -40466,8 +40755,11 @@
       <c r="E98" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F98" s="13">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="9">
         <v>44486</v>
       </c>
@@ -40483,8 +40775,11 @@
       <c r="E99" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F99" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="9">
         <v>44486</v>
       </c>
@@ -40500,8 +40795,11 @@
       <c r="E100" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F100" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="9">
         <v>44491</v>
       </c>
@@ -40517,8 +40815,11 @@
       <c r="E101" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F101" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="9">
         <v>44492</v>
       </c>
@@ -40534,8 +40835,11 @@
       <c r="E102" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F102" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="9">
         <v>44492</v>
       </c>
@@ -40551,8 +40855,11 @@
       <c r="E103" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F103" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
         <v>44493</v>
       </c>
@@ -40568,8 +40875,11 @@
       <c r="E104" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F104" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="9">
         <v>44493</v>
       </c>
@@ -40585,8 +40895,11 @@
       <c r="E105" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F105" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="9">
         <v>44493</v>
       </c>
@@ -40602,8 +40915,11 @@
       <c r="E106" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F106" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
         <v>44493</v>
       </c>
@@ -40619,8 +40935,11 @@
       <c r="E107" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F107" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="9">
         <v>44493</v>
       </c>
@@ -40636,8 +40955,11 @@
       <c r="E108" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F108" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
         <v>44493</v>
       </c>
@@ -40653,8 +40975,11 @@
       <c r="E109" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F109" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="9">
         <v>44493</v>
       </c>
@@ -40670,8 +40995,11 @@
       <c r="E110" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F110" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="9">
         <v>44496</v>
       </c>
@@ -40687,8 +41015,11 @@
       <c r="E111" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F111" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="9">
         <v>44498</v>
       </c>
@@ -40704,8 +41035,11 @@
       <c r="E112" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F112" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="9">
         <v>44499</v>
       </c>
@@ -40721,8 +41055,11 @@
       <c r="E113" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F113" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="9">
         <v>44499</v>
       </c>
@@ -40738,8 +41075,11 @@
       <c r="E114" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F114" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="9">
         <v>44500</v>
       </c>
@@ -40755,8 +41095,11 @@
       <c r="E115" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F115" s="13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="9">
         <v>44500</v>
       </c>
@@ -40772,8 +41115,11 @@
       <c r="E116" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F116" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="9">
         <v>44500</v>
       </c>
@@ -40789,8 +41135,11 @@
       <c r="E117" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F117" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="9">
         <v>44500</v>
       </c>
@@ -40806,8 +41155,11 @@
       <c r="E118" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F118" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="9">
         <v>44500</v>
       </c>
@@ -40823,8 +41175,11 @@
       <c r="E119" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F119" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="9">
         <v>44500</v>
       </c>
@@ -40840,8 +41195,11 @@
       <c r="E120" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F120" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="9">
         <v>44500</v>
       </c>
@@ -40857,8 +41215,11 @@
       <c r="E121" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F121" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="9">
         <v>44505</v>
       </c>
@@ -40874,8 +41235,11 @@
       <c r="E122" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F122" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="9">
         <v>44506</v>
       </c>
@@ -40891,8 +41255,11 @@
       <c r="E123" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F123" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="9">
         <v>44506</v>
       </c>
@@ -40908,8 +41275,11 @@
       <c r="E124" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F124" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="9">
         <v>44507</v>
       </c>
@@ -40925,8 +41295,11 @@
       <c r="E125" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F125" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="9">
         <v>44507</v>
       </c>
@@ -40942,8 +41315,11 @@
       <c r="E126" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F126" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="9">
         <v>44507</v>
       </c>
@@ -40959,8 +41335,11 @@
       <c r="E127" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F127" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="9">
         <v>44507</v>
       </c>
@@ -40976,8 +41355,11 @@
       <c r="E128" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F128" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="9">
         <v>44507</v>
       </c>
@@ -40993,8 +41375,11 @@
       <c r="E129" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F129" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="9">
         <v>44507</v>
       </c>
@@ -41010,8 +41395,11 @@
       <c r="E130" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F130" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="9">
         <v>44507</v>
       </c>
@@ -41027,8 +41415,11 @@
       <c r="E131" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F131" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="9">
         <v>44519</v>
       </c>
@@ -41044,8 +41435,11 @@
       <c r="E132" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F132" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="9">
         <v>44520</v>
       </c>
@@ -41061,8 +41455,11 @@
       <c r="E133" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F133" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="9">
         <v>44520</v>
       </c>
@@ -41078,8 +41475,11 @@
       <c r="E134" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F134" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="9">
         <v>44521</v>
       </c>
@@ -41095,8 +41495,11 @@
       <c r="E135" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F135" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="9">
         <v>44521</v>
       </c>
@@ -41112,8 +41515,11 @@
       <c r="E136" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F136" s="13">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="9">
         <v>44521</v>
       </c>
@@ -41129,8 +41535,11 @@
       <c r="E137" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F137" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="9">
         <v>44521</v>
       </c>
@@ -41146,8 +41555,11 @@
       <c r="E138" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F138" s="13">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="9">
         <v>44521</v>
       </c>
@@ -41163,8 +41575,11 @@
       <c r="E139" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F139" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="9">
         <v>44521</v>
       </c>
@@ -41180,8 +41595,11 @@
       <c r="E140" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F140" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="9">
         <v>44526</v>
       </c>
@@ -41197,8 +41615,11 @@
       <c r="E141" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F141" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="9">
         <v>44527</v>
       </c>
@@ -41214,8 +41635,11 @@
       <c r="E142" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F142" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="9">
         <v>44527</v>
       </c>
@@ -41231,8 +41655,11 @@
       <c r="E143" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F143" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="9">
         <v>44528</v>
       </c>
@@ -41248,8 +41675,11 @@
       <c r="E144" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F144" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="9">
         <v>44528</v>
       </c>
@@ -41265,8 +41695,11 @@
       <c r="E145" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F145" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="9">
         <v>44528</v>
       </c>
@@ -41282,8 +41715,11 @@
       <c r="E146" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F146" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="9">
         <v>44528</v>
       </c>
@@ -41299,8 +41735,11 @@
       <c r="E147" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F147" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="9">
         <v>44528</v>
       </c>
@@ -41316,8 +41755,11 @@
       <c r="E148" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F148" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="9">
         <v>44528</v>
       </c>
@@ -41333,8 +41775,11 @@
       <c r="E149" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F149" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="9">
         <v>44528</v>
       </c>
@@ -41350,8 +41795,11 @@
       <c r="E150" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F150" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="9">
         <v>44531</v>
       </c>
@@ -41367,8 +41815,11 @@
       <c r="E151" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F151" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="9">
         <v>44531</v>
       </c>
@@ -41384,8 +41835,11 @@
       <c r="E152" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F152" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="9">
         <v>44531</v>
       </c>
@@ -41401,8 +41855,11 @@
       <c r="E153" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F153" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="9">
         <v>44531</v>
       </c>
@@ -41418,8 +41875,11 @@
       <c r="E154" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F154" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="9">
         <v>44531</v>
       </c>
@@ -41435,8 +41895,11 @@
       <c r="E155" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F155" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="9">
         <v>44531</v>
       </c>
@@ -41452,8 +41915,11 @@
       <c r="E156" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F156" s="13">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="9">
         <v>44531</v>
       </c>
@@ -41469,8 +41935,11 @@
       <c r="E157" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F157" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="9">
         <v>44531</v>
       </c>
@@ -41486,8 +41955,11 @@
       <c r="E158" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F158" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="9">
         <v>44531</v>
       </c>
@@ -41503,8 +41975,11 @@
       <c r="E159" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F159" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="9">
         <v>44531</v>
       </c>
@@ -41520,8 +41995,11 @@
       <c r="E160" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F160" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="9">
         <v>44534</v>
       </c>
@@ -41537,8 +42015,11 @@
       <c r="E161" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F161" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="9">
         <v>44534</v>
       </c>
@@ -41554,8 +42035,11 @@
       <c r="E162" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F162" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="9">
         <v>44534</v>
       </c>
@@ -41571,8 +42055,11 @@
       <c r="E163" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F163" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="9">
         <v>44535</v>
       </c>
@@ -41588,8 +42075,11 @@
       <c r="E164" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F164" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="9">
         <v>44535</v>
       </c>
@@ -41605,8 +42095,11 @@
       <c r="E165" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F165" s="13">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="9">
         <v>44535</v>
       </c>
@@ -41622,8 +42115,11 @@
       <c r="E166" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F166" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="9">
         <v>44535</v>
       </c>
@@ -41639,8 +42135,11 @@
       <c r="E167" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F167" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="9">
         <v>44535</v>
       </c>
@@ -41656,8 +42155,11 @@
       <c r="E168" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F168" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="9">
         <v>44535</v>
       </c>
@@ -41673,8 +42175,11 @@
       <c r="E169" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F169" s="13">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="9">
         <v>44535</v>
       </c>
@@ -41690,8 +42195,11 @@
       <c r="E170" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F170" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="9">
         <v>44540</v>
       </c>
@@ -41707,8 +42215,11 @@
       <c r="E171" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F171" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="9">
         <v>44541</v>
       </c>
@@ -41724,8 +42235,11 @@
       <c r="E172" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F172" s="13">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="9">
         <v>44541</v>
       </c>
@@ -41741,8 +42255,11 @@
       <c r="E173" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F173" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="9">
         <v>44542</v>
       </c>
@@ -41758,8 +42275,11 @@
       <c r="E174" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F174" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="9">
         <v>44542</v>
       </c>
@@ -41775,8 +42295,11 @@
       <c r="E175" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F175" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="9">
         <v>44542</v>
       </c>
@@ -41792,8 +42315,11 @@
       <c r="E176" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F176" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="9">
         <v>44542</v>
       </c>
@@ -41809,8 +42335,11 @@
       <c r="E177" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F177" s="13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="9">
         <v>44542</v>
       </c>
@@ -41826,8 +42355,11 @@
       <c r="E178" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F178" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="9">
         <v>44542</v>
       </c>
@@ -41843,8 +42375,11 @@
       <c r="E179" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F179" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="9">
         <v>44542</v>
       </c>
@@ -41860,8 +42395,11 @@
       <c r="E180" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F180" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="9">
         <v>44552</v>
       </c>
@@ -41877,8 +42415,11 @@
       <c r="E181" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F181" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="9">
         <v>44552</v>
       </c>
@@ -41894,8 +42435,11 @@
       <c r="E182" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F182" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="9">
         <v>44552</v>
       </c>
@@ -41911,8 +42455,11 @@
       <c r="E183" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F183" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="9">
         <v>44552</v>
       </c>
@@ -41928,8 +42475,11 @@
       <c r="E184" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F184" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="9">
         <v>44552</v>
       </c>
@@ -41945,8 +42495,11 @@
       <c r="E185" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F185" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="9">
         <v>44552</v>
       </c>
@@ -41962,8 +42515,11 @@
       <c r="E186" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F186" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="9">
         <v>44552</v>
       </c>
@@ -41979,8 +42535,11 @@
       <c r="E187" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F187" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="9">
         <v>44552</v>
       </c>
@@ -41996,8 +42555,11 @@
       <c r="E188" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F188" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="9">
         <v>44552</v>
       </c>
@@ -42013,8 +42575,11 @@
       <c r="E189" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F189" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="9">
         <v>44568</v>
       </c>
@@ -42030,8 +42595,11 @@
       <c r="E190" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F190" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="9">
         <v>44569</v>
       </c>
@@ -42047,8 +42615,11 @@
       <c r="E191" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F191" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="9">
         <v>44570</v>
       </c>
@@ -42064,8 +42635,11 @@
       <c r="E192" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F192" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="9">
         <v>44570</v>
       </c>
@@ -42081,8 +42655,11 @@
       <c r="E193" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F193" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="9">
         <v>44570</v>
       </c>
@@ -42098,8 +42675,11 @@
       <c r="E194" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F194" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="9">
         <v>44570</v>
       </c>
@@ -42115,8 +42695,11 @@
       <c r="E195" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F195" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="9">
         <v>44570</v>
       </c>
@@ -42132,8 +42715,11 @@
       <c r="E196" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F196" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="9">
         <v>44575</v>
       </c>
@@ -42149,8 +42735,11 @@
       <c r="E197" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F197" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="9">
         <v>44576</v>
       </c>
@@ -42166,8 +42755,11 @@
       <c r="E198" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F198" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="9">
         <v>44576</v>
       </c>
@@ -42183,8 +42775,11 @@
       <c r="E199" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F199" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="9">
         <v>44577</v>
       </c>
@@ -42200,8 +42795,11 @@
       <c r="E200" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F200" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="9">
         <v>44577</v>
       </c>
@@ -42217,8 +42815,11 @@
       <c r="E201" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F201" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="9">
         <v>44577</v>
       </c>
@@ -42234,8 +42835,11 @@
       <c r="E202" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F202" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="9">
         <v>44577</v>
       </c>
@@ -42251,8 +42855,11 @@
       <c r="E203" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F203" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="9">
         <v>44577</v>
       </c>
@@ -42268,8 +42875,11 @@
       <c r="E204" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F204" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="9">
         <v>44577</v>
       </c>
@@ -42285,8 +42895,11 @@
       <c r="E205" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F205" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="9">
         <v>44577</v>
       </c>
@@ -42302,8 +42915,11 @@
       <c r="E206" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F206" s="13">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="9">
         <v>44580</v>
       </c>
@@ -42319,8 +42935,11 @@
       <c r="E207" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F207" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="9">
         <v>44580</v>
       </c>
@@ -42336,8 +42955,11 @@
       <c r="E208" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F208" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="9">
         <v>44580</v>
       </c>
@@ -42353,8 +42975,11 @@
       <c r="E209" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F209" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="9">
         <v>44582</v>
       </c>
@@ -42370,8 +42995,11 @@
       <c r="E210" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F210" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="9">
         <v>44583</v>
       </c>
@@ -42387,8 +43015,11 @@
       <c r="E211" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F211" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="9">
         <v>44583</v>
       </c>
@@ -42404,8 +43035,11 @@
       <c r="E212" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F212" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="9">
         <v>44584</v>
       </c>
@@ -42421,8 +43055,11 @@
       <c r="E213" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F213" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="9">
         <v>44584</v>
       </c>
@@ -42438,8 +43075,11 @@
       <c r="E214" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F214" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="9">
         <v>44584</v>
       </c>
@@ -42455,8 +43095,11 @@
       <c r="E215" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F215" s="13">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="9">
         <v>44584</v>
       </c>
@@ -42472,8 +43115,11 @@
       <c r="E216" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F216" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="9">
         <v>44584</v>
       </c>
@@ -42489,8 +43135,11 @@
       <c r="E217" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F217" s="13">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="9">
         <v>44584</v>
       </c>
@@ -42506,8 +43155,11 @@
       <c r="E218" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F218" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="9">
         <v>44584</v>
       </c>
@@ -42523,8 +43175,11 @@
       <c r="E219" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F219" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="9">
         <v>44587</v>
       </c>
@@ -42540,8 +43195,11 @@
       <c r="E220" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F220" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="9">
         <v>44593</v>
       </c>
@@ -42557,8 +43215,11 @@
       <c r="E221" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F221" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="9">
         <v>44596</v>
       </c>
@@ -42574,8 +43235,11 @@
       <c r="E222" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F222" s="13">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="9">
         <v>44597</v>
       </c>
@@ -42591,8 +43255,11 @@
       <c r="E223" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F223" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="9">
         <v>44597</v>
       </c>
@@ -42608,8 +43275,11 @@
       <c r="E224" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F224" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="9">
         <v>44598</v>
       </c>
@@ -42625,8 +43295,11 @@
       <c r="E225" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F225" s="13">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="9">
         <v>44598</v>
       </c>
@@ -42642,8 +43315,11 @@
       <c r="E226" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F226" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="9">
         <v>44598</v>
       </c>
@@ -42659,8 +43335,11 @@
       <c r="E227" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F227" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="9">
         <v>44598</v>
       </c>
@@ -42676,8 +43355,11 @@
       <c r="E228" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F228" s="13">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="9">
         <v>44598</v>
       </c>
@@ -42693,8 +43375,11 @@
       <c r="E229" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F229" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="9">
         <v>44598</v>
       </c>
@@ -42710,8 +43395,11 @@
       <c r="E230" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F230" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="9">
         <v>44598</v>
       </c>
@@ -42727,8 +43415,11 @@
       <c r="E231" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F231" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="9">
         <v>44603</v>
       </c>
@@ -42744,8 +43435,11 @@
       <c r="E232" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F232" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="9">
         <v>44604</v>
       </c>
@@ -42761,8 +43455,11 @@
       <c r="E233" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F233" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="9">
         <v>44604</v>
       </c>
@@ -42778,8 +43475,11 @@
       <c r="E234" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F234" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="9">
         <v>44605</v>
       </c>
@@ -42795,8 +43495,11 @@
       <c r="E235" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F235" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="9">
         <v>44605</v>
       </c>
@@ -42812,8 +43515,11 @@
       <c r="E236" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F236" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="9">
         <v>44605</v>
       </c>
@@ -42829,8 +43535,11 @@
       <c r="E237" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F237" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="9">
         <v>44605</v>
       </c>
@@ -42846,8 +43555,11 @@
       <c r="E238" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F238" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="9">
         <v>44605</v>
       </c>
@@ -42863,8 +43575,11 @@
       <c r="E239" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F239" s="13">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="9">
         <v>44605</v>
       </c>
@@ -42880,8 +43595,11 @@
       <c r="E240" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F240" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="9">
         <v>44605</v>
       </c>
@@ -42897,8 +43615,11 @@
       <c r="E241" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F241" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="9">
         <v>44610</v>
       </c>
@@ -42914,8 +43635,11 @@
       <c r="E242" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F242" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="9">
         <v>44611</v>
       </c>
@@ -42931,8 +43655,11 @@
       <c r="E243" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F243" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="9">
         <v>44611</v>
       </c>
@@ -42948,8 +43675,11 @@
       <c r="E244" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F244" s="13">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="9">
         <v>44612</v>
       </c>
@@ -42965,8 +43695,11 @@
       <c r="E245" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F245" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="9">
         <v>44612</v>
       </c>
@@ -42982,8 +43715,11 @@
       <c r="E246" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F246" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="9">
         <v>44612</v>
       </c>
@@ -42999,8 +43735,11 @@
       <c r="E247" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F247" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="9">
         <v>44612</v>
       </c>
@@ -43016,8 +43755,11 @@
       <c r="E248" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F248" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="9">
         <v>44612</v>
       </c>
@@ -43033,8 +43775,11 @@
       <c r="E249" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F249" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="9">
         <v>44612</v>
       </c>
@@ -43050,8 +43795,11 @@
       <c r="E250" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F250" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="9">
         <v>44612</v>
       </c>
@@ -43067,8 +43815,11 @@
       <c r="E251" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F251" s="13">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="9">
         <v>44617</v>
       </c>
@@ -43084,8 +43835,11 @@
       <c r="E252" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F252" s="13">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="9">
         <v>44618</v>
       </c>
@@ -43101,8 +43855,11 @@
       <c r="E253" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F253" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="9">
         <v>44618</v>
       </c>
@@ -43118,8 +43875,11 @@
       <c r="E254" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F254" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="9">
         <v>44619</v>
       </c>
@@ -43135,8 +43895,11 @@
       <c r="E255" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F255" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="9">
         <v>44619</v>
       </c>
@@ -43152,8 +43915,11 @@
       <c r="E256" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F256" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="9">
         <v>44619</v>
       </c>
@@ -43169,8 +43935,11 @@
       <c r="E257" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F257" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="9">
         <v>44619</v>
       </c>
@@ -43186,8 +43955,11 @@
       <c r="E258" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F258" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="9">
         <v>44619</v>
       </c>
@@ -43203,8 +43975,11 @@
       <c r="E259" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F259" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="9">
         <v>44619</v>
       </c>
@@ -43220,8 +43995,11 @@
       <c r="E260" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F260" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="9">
         <v>44619</v>
       </c>
@@ -43237,8 +44015,11 @@
       <c r="E261" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F261" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="9">
         <v>44624</v>
       </c>
@@ -43254,8 +44035,11 @@
       <c r="E262" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F262" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="9">
         <v>44625</v>
       </c>
@@ -43271,8 +44055,11 @@
       <c r="E263" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F263" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="9">
         <v>44625</v>
       </c>
@@ -43288,8 +44075,11 @@
       <c r="E264" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F264" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="9">
         <v>44626</v>
       </c>
@@ -43305,8 +44095,11 @@
       <c r="E265" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F265" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="9">
         <v>44626</v>
       </c>
@@ -43322,8 +44115,11 @@
       <c r="E266" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F266" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="9">
         <v>44626</v>
       </c>
@@ -43339,8 +44135,11 @@
       <c r="E267" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F267" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="9">
         <v>44626</v>
       </c>
@@ -43356,8 +44155,11 @@
       <c r="E268" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F268" s="13">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="9">
         <v>44626</v>
       </c>
@@ -43373,8 +44175,11 @@
       <c r="E269" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F269" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="9">
         <v>44626</v>
       </c>
@@ -43390,8 +44195,11 @@
       <c r="E270" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F270" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="9">
         <v>44626</v>
       </c>
@@ -43407,8 +44215,11 @@
       <c r="E271" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F271" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="9">
         <v>44631</v>
       </c>
@@ -43424,8 +44235,11 @@
       <c r="E272" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F272" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="9">
         <v>44632</v>
       </c>
@@ -43441,8 +44255,11 @@
       <c r="E273" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F273" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="9">
         <v>44632</v>
       </c>
@@ -43458,8 +44275,11 @@
       <c r="E274" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F274" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="9">
         <v>44633</v>
       </c>
@@ -43475,8 +44295,11 @@
       <c r="E275" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F275" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="9">
         <v>44633</v>
       </c>
@@ -43492,8 +44315,11 @@
       <c r="E276" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F276" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="9">
         <v>44633</v>
       </c>
@@ -43509,8 +44335,11 @@
       <c r="E277" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F277" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="9">
         <v>44633</v>
       </c>
@@ -43526,8 +44355,11 @@
       <c r="E278" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F278" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="9">
         <v>44633</v>
       </c>
@@ -43543,8 +44375,11 @@
       <c r="E279" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F279" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="9">
         <v>44633</v>
       </c>
@@ -43560,8 +44395,11 @@
       <c r="E280" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F280" s="13">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="9">
         <v>44633</v>
       </c>
@@ -43577,8 +44415,11 @@
       <c r="E281" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F281" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="9">
         <v>44638</v>
       </c>
@@ -43594,8 +44435,11 @@
       <c r="E282" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F282" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="9">
         <v>44639</v>
       </c>
@@ -43611,8 +44455,11 @@
       <c r="E283" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F283" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="9">
         <v>44639</v>
       </c>
@@ -43628,8 +44475,11 @@
       <c r="E284" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F284" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="9">
         <v>44640</v>
       </c>
@@ -43645,8 +44495,11 @@
       <c r="E285" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F285" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="9">
         <v>44640</v>
       </c>
@@ -43662,8 +44515,11 @@
       <c r="E286" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F286" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="9">
         <v>44640</v>
       </c>
@@ -43679,8 +44535,11 @@
       <c r="E287" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F287" s="13">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="9">
         <v>44640</v>
       </c>
@@ -43696,8 +44555,11 @@
       <c r="E288" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F288" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="9">
         <v>44640</v>
       </c>
@@ -43713,8 +44575,11 @@
       <c r="E289" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F289" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="9">
         <v>44640</v>
       </c>
@@ -43730,8 +44595,11 @@
       <c r="E290" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F290" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="9">
         <v>44640</v>
       </c>
@@ -43747,8 +44615,11 @@
       <c r="E291" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F291" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="9">
         <v>44653</v>
       </c>
@@ -43764,8 +44635,11 @@
       <c r="E292" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F292" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="9">
         <v>44653</v>
       </c>
@@ -43781,8 +44655,11 @@
       <c r="E293" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F293" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="9">
         <v>44654</v>
       </c>
@@ -43798,8 +44675,11 @@
       <c r="E294" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F294" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="9">
         <v>44654</v>
       </c>
@@ -43815,8 +44695,11 @@
       <c r="E295" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F295" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="9">
         <v>44654</v>
       </c>
@@ -43832,8 +44715,11 @@
       <c r="E296" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F296" s="13">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="9">
         <v>44654</v>
       </c>
@@ -43849,8 +44735,11 @@
       <c r="E297" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F297" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="9">
         <v>44654</v>
       </c>
@@ -43866,8 +44755,11 @@
       <c r="E298" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F298" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="9">
         <v>44654</v>
       </c>
@@ -43883,8 +44775,11 @@
       <c r="E299" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F299" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="9">
         <v>44654</v>
       </c>
@@ -43900,8 +44795,11 @@
       <c r="E300" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F300" s="13">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="9">
         <v>44654</v>
       </c>
@@ -43917,8 +44815,11 @@
       <c r="E301" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F301" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="9">
         <v>44659</v>
       </c>
@@ -43934,8 +44835,11 @@
       <c r="E302" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F302" s="13">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="9">
         <v>44660</v>
       </c>
@@ -43951,8 +44855,11 @@
       <c r="E303" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F303" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="9">
         <v>44660</v>
       </c>
@@ -43968,8 +44875,11 @@
       <c r="E304" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F304" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="9">
         <v>44661</v>
       </c>
@@ -43985,8 +44895,11 @@
       <c r="E305" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F305" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="9">
         <v>44661</v>
       </c>
@@ -44002,8 +44915,11 @@
       <c r="E306" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F306" s="13">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="9">
         <v>44661</v>
       </c>
@@ -44019,8 +44935,11 @@
       <c r="E307" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F307" s="13">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="9">
         <v>44661</v>
       </c>
@@ -44036,8 +44955,11 @@
       <c r="E308" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F308" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="9">
         <v>44661</v>
       </c>
@@ -44053,8 +44975,11 @@
       <c r="E309" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F309" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="9">
         <v>44661</v>
       </c>
@@ -44070,8 +44995,11 @@
       <c r="E310" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F310" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="9">
         <v>44661</v>
       </c>
@@ -44087,8 +45015,11 @@
       <c r="E311" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F311" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="9">
         <v>44666</v>
       </c>
@@ -44104,8 +45035,11 @@
       <c r="E312" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F312" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="9">
         <v>44667</v>
       </c>
@@ -44121,8 +45055,11 @@
       <c r="E313" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F313" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="9">
         <v>44667</v>
       </c>
@@ -44138,8 +45075,11 @@
       <c r="E314" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F314" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="9">
         <v>44668</v>
       </c>
@@ -44155,8 +45095,11 @@
       <c r="E315" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F315" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="9">
         <v>44668</v>
       </c>
@@ -44172,8 +45115,11 @@
       <c r="E316" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F316" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="9">
         <v>44668</v>
       </c>
@@ -44189,8 +45135,11 @@
       <c r="E317" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F317" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="9">
         <v>44668</v>
       </c>
@@ -44206,8 +45155,11 @@
       <c r="E318" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F318" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="9">
         <v>44668</v>
       </c>
@@ -44223,8 +45175,11 @@
       <c r="E319" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F319" s="13">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="9">
         <v>44668</v>
       </c>
@@ -44240,8 +45195,11 @@
       <c r="E320" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F320" s="13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="9">
         <v>44668</v>
       </c>
@@ -44257,8 +45215,11 @@
       <c r="E321" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F321" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="9">
         <v>44671</v>
       </c>
@@ -44274,8 +45235,11 @@
       <c r="E322" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F322" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="9">
         <v>44671</v>
       </c>
@@ -44291,8 +45255,11 @@
       <c r="E323" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F323" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="9">
         <v>44671</v>
       </c>
@@ -44308,8 +45275,11 @@
       <c r="E324" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F324" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="9">
         <v>44671</v>
       </c>
@@ -44325,8 +45295,11 @@
       <c r="E325" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F325" s="13">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="9">
         <v>44671</v>
       </c>
@@ -44342,8 +45315,11 @@
       <c r="E326" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F326" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="9">
         <v>44671</v>
       </c>
@@ -44359,8 +45335,11 @@
       <c r="E327" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F327" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="9">
         <v>44671</v>
       </c>
@@ -44376,8 +45355,11 @@
       <c r="E328" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F328" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="9">
         <v>44671</v>
       </c>
@@ -44393,8 +45375,11 @@
       <c r="E329" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F329" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="9">
         <v>44671</v>
       </c>
@@ -44410,8 +45395,11 @@
       <c r="E330" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F330" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="9">
         <v>44671</v>
       </c>
@@ -44427,8 +45415,11 @@
       <c r="E331" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F331" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="9">
         <v>44674</v>
       </c>
@@ -44444,8 +45435,11 @@
       <c r="E332" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F332" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="9">
         <v>44674</v>
       </c>
@@ -44461,8 +45455,11 @@
       <c r="E333" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F333" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="9">
         <v>44674</v>
       </c>
@@ -44478,8 +45475,11 @@
       <c r="E334" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F334" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="9">
         <v>44675</v>
       </c>
@@ -44495,8 +45495,11 @@
       <c r="E335" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F335" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="9">
         <v>44675</v>
       </c>
@@ -44512,8 +45515,11 @@
       <c r="E336" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F336" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="9">
         <v>44675</v>
       </c>
@@ -44529,8 +45535,11 @@
       <c r="E337" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F337" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="9">
         <v>44675</v>
       </c>
@@ -44546,8 +45555,11 @@
       <c r="E338" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F338" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="9">
         <v>44675</v>
       </c>
@@ -44563,8 +45575,11 @@
       <c r="E339" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F339" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="9">
         <v>44675</v>
       </c>
@@ -44580,8 +45595,11 @@
       <c r="E340" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F340" s="13">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="9">
         <v>44675</v>
       </c>
@@ -44597,8 +45615,11 @@
       <c r="E341" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F341" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="9">
         <v>44680</v>
       </c>
@@ -44614,8 +45635,11 @@
       <c r="E342" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F342" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="9">
         <v>44681</v>
       </c>
@@ -44631,8 +45655,11 @@
       <c r="E343" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F343" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="9">
         <v>44681</v>
       </c>
@@ -44648,8 +45675,11 @@
       <c r="E344" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F344" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="9">
         <v>44682</v>
       </c>
@@ -44665,8 +45695,11 @@
       <c r="E345" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F345" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="9">
         <v>44682</v>
       </c>
@@ -44682,8 +45715,11 @@
       <c r="E346" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F346" s="13">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="9">
         <v>44682</v>
       </c>
@@ -44699,8 +45735,11 @@
       <c r="E347" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F347" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="9">
         <v>44682</v>
       </c>
@@ -44716,8 +45755,11 @@
       <c r="E348" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F348" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="9">
         <v>44682</v>
       </c>
@@ -44733,8 +45775,11 @@
       <c r="E349" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F349" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="9">
         <v>44682</v>
       </c>
@@ -44750,8 +45795,11 @@
       <c r="E350" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F350" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="9">
         <v>44682</v>
       </c>
@@ -44767,8 +45815,11 @@
       <c r="E351" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F351" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="9">
         <v>44687</v>
       </c>
@@ -44784,8 +45835,11 @@
       <c r="E352" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F352" s="13">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="9">
         <v>44688</v>
       </c>
@@ -44801,8 +45855,11 @@
       <c r="E353" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F353" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="9">
         <v>44689</v>
       </c>
@@ -44818,8 +45875,11 @@
       <c r="E354" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F354" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="9">
         <v>44689</v>
       </c>
@@ -44835,8 +45895,11 @@
       <c r="E355" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F355" s="13">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="9">
         <v>44689</v>
       </c>
@@ -44852,8 +45915,11 @@
       <c r="E356" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F356" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="9">
         <v>44689</v>
       </c>
@@ -44869,8 +45935,11 @@
       <c r="E357" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F357" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="9">
         <v>44689</v>
       </c>
@@ -44886,8 +45955,11 @@
       <c r="E358" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F358" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="9">
         <v>44689</v>
       </c>
@@ -44903,8 +45975,11 @@
       <c r="E359" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F359" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" s="9">
         <v>44692</v>
       </c>
@@ -44920,8 +45995,11 @@
       <c r="E360" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F360" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" s="9">
         <v>44692</v>
       </c>
@@ -44937,8 +46015,11 @@
       <c r="E361" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F361" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" s="9">
         <v>44695</v>
       </c>
@@ -44954,8 +46035,11 @@
       <c r="E362" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F362" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" s="9">
         <v>44695</v>
       </c>
@@ -44971,8 +46055,11 @@
       <c r="E363" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F363" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" s="9">
         <v>44695</v>
       </c>
@@ -44988,8 +46075,11 @@
       <c r="E364" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F364" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="9">
         <v>44695</v>
       </c>
@@ -45005,8 +46095,11 @@
       <c r="E365" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F365" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" s="9">
         <v>44695</v>
       </c>
@@ -45022,8 +46115,11 @@
       <c r="E366" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F366" s="13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" s="9">
         <v>44695</v>
       </c>
@@ -45039,8 +46135,11 @@
       <c r="E367" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F367" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="9">
         <v>44695</v>
       </c>
@@ -45056,8 +46155,11 @@
       <c r="E368" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F368" s="13">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="9">
         <v>44695</v>
       </c>
@@ -45073,8 +46175,11 @@
       <c r="E369" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F369" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="9">
         <v>44695</v>
       </c>
@@ -45090,8 +46195,11 @@
       <c r="E370" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F370" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="9">
         <v>44695</v>
       </c>
@@ -45107,8 +46215,11 @@
       <c r="E371" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F371" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="9">
         <v>44702</v>
       </c>
@@ -45124,8 +46235,11 @@
       <c r="E372" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F372" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="9">
         <v>44702</v>
       </c>
@@ -45141,8 +46255,11 @@
       <c r="E373" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F373" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="9">
         <v>44702</v>
       </c>
@@ -45158,8 +46275,11 @@
       <c r="E374" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F374" s="13">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="9">
         <v>44702</v>
       </c>
@@ -45175,8 +46295,11 @@
       <c r="E375" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F375" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="9">
         <v>44702</v>
       </c>
@@ -45192,8 +46315,11 @@
       <c r="E376" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F376" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="9">
         <v>44702</v>
       </c>
@@ -45209,8 +46335,11 @@
       <c r="E377" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F377" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="9">
         <v>44702</v>
       </c>
@@ -45226,8 +46355,11 @@
       <c r="E378" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F378" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="9">
         <v>44702</v>
       </c>
@@ -45243,8 +46375,11 @@
       <c r="E379" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F379" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="9">
         <v>44702</v>
       </c>
@@ -45260,8 +46395,11 @@
       <c r="E380" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F380" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="9">
         <v>44702</v>
       </c>
@@ -45276,6 +46414,9 @@
       </c>
       <c r="E381" t="s">
         <v>45</v>
+      </c>
+      <c r="F381" s="13">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
